--- a/artfynd/A 18632-2026 artfynd.xlsx
+++ b/artfynd/A 18632-2026 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>58060447</v>
+        <v>58060477</v>
       </c>
       <c r="B2" t="n">
-        <v>57505</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>206002</v>
+        <v>102102</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Mustaschfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Myotis mystacinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>577683.2038139515</v>
+        <v>577683</v>
       </c>
       <c r="R2" t="n">
-        <v>6784683.651547736</v>
+        <v>6784684</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -752,19 +747,9 @@
           <t>2005-08-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2005-08-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,12 +780,7 @@
         <v>58060556</v>
       </c>
       <c r="B3" t="n">
-        <v>57491</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>577683.2038139515</v>
+        <v>577683</v>
       </c>
       <c r="R3" t="n">
-        <v>6784683.651547736</v>
+        <v>6784684</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -869,19 +849,9 @@
           <t>2005-07-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2005-07-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,12 +882,7 @@
         <v>58060480</v>
       </c>
       <c r="B4" t="n">
-        <v>57484</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -953,10 +918,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>577683.2038139515</v>
+        <v>577683</v>
       </c>
       <c r="R4" t="n">
-        <v>6784683.651547736</v>
+        <v>6784684</v>
       </c>
       <c r="S4" t="n">
         <v>50</v>
@@ -986,19 +951,9 @@
           <t>2005-07-01</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2005-07-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,37 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>58060477</v>
+        <v>58060447</v>
       </c>
       <c r="B5" t="n">
-        <v>57493</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Dokumentation efterfrågas</t>
-        </is>
+        <v>56837</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102102</v>
+        <v>206002</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mustaschfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Myotis mystacinus</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1070,10 +1020,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>577683.2038139515</v>
+        <v>577683</v>
       </c>
       <c r="R5" t="n">
-        <v>6784683.651547736</v>
+        <v>6784684</v>
       </c>
       <c r="S5" t="n">
         <v>50</v>
@@ -1103,19 +1053,9 @@
           <t>2005-08-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2005-08-01</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 18632-2026 artfynd.xlsx
+++ b/artfynd/A 18632-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58060477</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58060556</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58060480</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,8 +1100,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58060447</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>